--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-severite.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-severite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5089,7 +5089,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>175</v>
       </c>
@@ -5104,13 +5104,13 @@
         <v>62</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5192,7 +5192,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>179</v>
       </c>
@@ -5207,13 +5207,13 @@
         <v>180</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5501,7 +5501,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>193</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>

--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-severite.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-severite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
